--- a/从零开始学Slots/从零开始学Slots-24-数值篇-StickyWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-24-数值篇-StickyWild.xlsx
@@ -9307,6 +9307,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:I165" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -11582,5 +11585,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:P155" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-24-数值篇-StickyWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-24-数值篇-StickyWild.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="250">
   <si>
     <r>
       <rPr>
@@ -8229,7 +8229,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8372,6 +8372,22 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -9373,8 +9389,8 @@
       <c r="B5" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>117</v>
+      <c r="C5" s="36">
+        <v>1</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -9435,8 +9451,8 @@
       <c r="B10" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>127</v>
+      <c r="C10" s="36">
+        <v>5</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
@@ -9490,14 +9506,14 @@
       <c r="A15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>136</v>
+      <c r="B15" s="37">
+        <v>9</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>136</v>
+      <c r="D15" s="37">
+        <v>9</v>
       </c>
       <c r="G15" s="17" t="s">
         <v>138</v>
@@ -9508,11 +9524,11 @@
       <c r="A16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>139</v>
+      <c r="B16" s="37">
+        <v>10</v>
+      </c>
+      <c r="C16" s="37">
+        <v>10</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>137</v>
@@ -9592,11 +9608,11 @@
       <c r="A22" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>136</v>
+      <c r="B22" s="37">
+        <v>9</v>
+      </c>
+      <c r="C22" s="37">
+        <v>9</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>137</v>
@@ -9606,14 +9622,14 @@
       <c r="A23" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>139</v>
+      <c r="B23" s="37">
+        <v>10</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>139</v>
+      <c r="D23" s="37">
+        <v>10</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9714,8 +9730,8 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
-        <v>136</v>
+      <c r="A31" s="38">
+        <v>9</v>
       </c>
       <c r="B31" s="18" t="n">
         <f aca="false">COUNTIF(B15:B26,"9")+COUNTIF(B15:B26,"Wild")</f>
@@ -9746,8 +9762,8 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
-        <v>139</v>
+      <c r="A32" s="38">
+        <v>10</v>
       </c>
       <c r="B32" s="18" t="n">
         <f aca="false">COUNTIF(B15:B26,"10")+COUNTIF(B15:B26,"Wild")</f>
@@ -9982,8 +9998,8 @@
       <c r="A45" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B45" s="15" t="s">
-        <v>136</v>
+      <c r="B45" s="37">
+        <v>9</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>143</v>
@@ -10000,8 +10016,8 @@
       <c r="A46" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="15" t="s">
-        <v>139</v>
+      <c r="B46" s="37">
+        <v>10</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>143</v>
@@ -10084,28 +10100,28 @@
       <c r="A52" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B52" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>136</v>
+      <c r="B52" s="37">
+        <v>9</v>
+      </c>
+      <c r="C52" s="37">
+        <v>9</v>
+      </c>
+      <c r="D52" s="37">
+        <v>9</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B53" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>139</v>
+      <c r="B53" s="37">
+        <v>10</v>
+      </c>
+      <c r="C53" s="37">
+        <v>10</v>
+      </c>
+      <c r="D53" s="37">
+        <v>10</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10467,8 +10483,8 @@
       <c r="C78" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="20" t="s">
-        <v>185</v>
+      <c r="H78" s="38">
+        <v>1</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10606,8 +10622,8 @@
       <c r="C84" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H84" s="20" t="s">
-        <v>185</v>
+      <c r="H84" s="38">
+        <v>1</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10745,8 +10761,8 @@
       <c r="C90" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H90" s="20" t="s">
-        <v>185</v>
+      <c r="H90" s="38">
+        <v>1</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10884,8 +10900,8 @@
       <c r="C96" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H96" s="20" t="s">
-        <v>185</v>
+      <c r="H96" s="38">
+        <v>1</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11316,8 +11332,8 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="29" t="s">
-        <v>218</v>
+      <c r="A116" s="39">
+        <v>10</v>
       </c>
       <c r="B116" s="29"/>
       <c r="F116" s="22" t="n">

--- a/从零开始学Slots/从零开始学Slots-24-数值篇-StickyWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-24-数值篇-StickyWild.xlsx
@@ -8040,12 +8040,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.0000%"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -8229,7 +8230,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8387,6 +8388,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9749,7 +9758,7 @@
         <f aca="false">B31*C31*D31</f>
         <v>8</v>
       </c>
-      <c r="F31" s="21" t="n">
+      <c r="F31" s="40" t="n">
         <f aca="false">E31/$B$8</f>
         <v>0.00462962962962963</v>
       </c>
@@ -9781,7 +9790,7 @@
         <f aca="false">B32*C32*D32</f>
         <v>8</v>
       </c>
-      <c r="F32" s="21" t="n">
+      <c r="F32" s="40" t="n">
         <f aca="false">E32/$B$8</f>
         <v>0.00462962962962963</v>
       </c>
@@ -9813,7 +9822,7 @@
         <f aca="false">B33*C33*D33</f>
         <v>18</v>
       </c>
-      <c r="F33" s="21" t="n">
+      <c r="F33" s="40" t="n">
         <f aca="false">E33/$B$8</f>
         <v>0.0104166666666667</v>
       </c>
@@ -9845,7 +9854,7 @@
         <f aca="false">B34*C34*D34</f>
         <v>18</v>
       </c>
-      <c r="F34" s="21" t="n">
+      <c r="F34" s="40" t="n">
         <f aca="false">E34/$B$8</f>
         <v>0.0104166666666667</v>
       </c>
@@ -9877,7 +9886,7 @@
         <f aca="false">B35*C35*D35</f>
         <v>27</v>
       </c>
-      <c r="F35" s="21" t="n">
+      <c r="F35" s="40" t="n">
         <f aca="false">E35/$B$8</f>
         <v>0.015625</v>
       </c>
@@ -9959,7 +9968,7 @@
         <f aca="false">$B$8</f>
         <v>1728</v>
       </c>
-      <c r="E41" s="25" t="n">
+      <c r="E41" s="41" t="n">
         <f aca="false">C41/D41</f>
         <v>0.00520833333333333</v>
       </c>
@@ -10219,15 +10228,15 @@
       <c r="A61" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B61" s="21" t="n">
+      <c r="B61" s="40" t="n">
         <f aca="false">COUNTIF(B45:B56,"Wild")/B57</f>
         <v>0</v>
       </c>
-      <c r="C61" s="21" t="n">
+      <c r="C61" s="40" t="n">
         <f aca="false">COUNTIF(C45:C56,"Wild")/C57</f>
         <v>0.5</v>
       </c>
-      <c r="D61" s="21" t="n">
+      <c r="D61" s="40" t="n">
         <f aca="false">COUNTIF(D45:D56,"Wild")/D57</f>
         <v>0.5</v>
       </c>
@@ -10241,15 +10250,15 @@
       <c r="A62" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B62" s="21" t="n">
+      <c r="B62" s="40" t="n">
         <f aca="false">1-B61</f>
         <v>1</v>
       </c>
-      <c r="C62" s="21" t="n">
+      <c r="C62" s="40" t="n">
         <f aca="false">1-C61</f>
         <v>0.5</v>
       </c>
-      <c r="D62" s="21" t="n">
+      <c r="D62" s="40" t="n">
         <f aca="false">1-D61</f>
         <v>0.5</v>
       </c>
@@ -11081,19 +11090,19 @@
       <c r="A106" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B106" s="25" t="n">
+      <c r="B106" s="41" t="n">
         <f aca="false">$C$62^(A106-1)*$D$62^(A106-1)</f>
         <v>1</v>
       </c>
-      <c r="C106" s="25" t="n">
+      <c r="C106" s="41" t="n">
         <f aca="false">(1-$C$62^(A106-1))*$D$62^(A106-1)</f>
         <v>0</v>
       </c>
-      <c r="D106" s="25" t="n">
+      <c r="D106" s="41" t="n">
         <f aca="false">$C$62^(A106-1)*(1-$D$62^(A106-1))</f>
         <v>0</v>
       </c>
-      <c r="E106" s="25" t="n">
+      <c r="E106" s="41" t="n">
         <f aca="false">(1-$C$62^(A106-1))*(1-$D$62^(A106-1))</f>
         <v>0</v>
       </c>
@@ -11110,19 +11119,19 @@
       <c r="A107" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B107" s="25" t="n">
+      <c r="B107" s="41" t="n">
         <f aca="false">$C$62^(A107-1)*$D$62^(A107-1)</f>
         <v>0.25</v>
       </c>
-      <c r="C107" s="25" t="n">
+      <c r="C107" s="41" t="n">
         <f aca="false">(1-$C$62^(A107-1))*$D$62^(A107-1)</f>
         <v>0.25</v>
       </c>
-      <c r="D107" s="25" t="n">
+      <c r="D107" s="41" t="n">
         <f aca="false">$C$62^(A107-1)*(1-$D$62^(A107-1))</f>
         <v>0.25</v>
       </c>
-      <c r="E107" s="25" t="n">
+      <c r="E107" s="41" t="n">
         <f aca="false">(1-$C$62^(A107-1))*(1-$D$62^(A107-1))</f>
         <v>0.25</v>
       </c>
@@ -11135,19 +11144,19 @@
       <c r="A108" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B108" s="25" t="n">
+      <c r="B108" s="41" t="n">
         <f aca="false">$C$62^(A108-1)*$D$62^(A108-1)</f>
         <v>0.0625</v>
       </c>
-      <c r="C108" s="25" t="n">
+      <c r="C108" s="41" t="n">
         <f aca="false">(1-$C$62^(A108-1))*$D$62^(A108-1)</f>
         <v>0.1875</v>
       </c>
-      <c r="D108" s="25" t="n">
+      <c r="D108" s="41" t="n">
         <f aca="false">$C$62^(A108-1)*(1-$D$62^(A108-1))</f>
         <v>0.1875</v>
       </c>
-      <c r="E108" s="25" t="n">
+      <c r="E108" s="41" t="n">
         <f aca="false">(1-$C$62^(A108-1))*(1-$D$62^(A108-1))</f>
         <v>0.5625</v>
       </c>
@@ -11160,19 +11169,19 @@
       <c r="A109" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B109" s="25" t="n">
+      <c r="B109" s="41" t="n">
         <f aca="false">$C$62^(A109-1)*$D$62^(A109-1)</f>
         <v>0.015625</v>
       </c>
-      <c r="C109" s="25" t="n">
+      <c r="C109" s="41" t="n">
         <f aca="false">(1-$C$62^(A109-1))*$D$62^(A109-1)</f>
         <v>0.109375</v>
       </c>
-      <c r="D109" s="25" t="n">
+      <c r="D109" s="41" t="n">
         <f aca="false">$C$62^(A109-1)*(1-$D$62^(A109-1))</f>
         <v>0.109375</v>
       </c>
-      <c r="E109" s="25" t="n">
+      <c r="E109" s="41" t="n">
         <f aca="false">(1-$C$62^(A109-1))*(1-$D$62^(A109-1))</f>
         <v>0.765625</v>
       </c>
@@ -11185,19 +11194,19 @@
       <c r="A110" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B110" s="25" t="n">
+      <c r="B110" s="41" t="n">
         <f aca="false">$C$62^(A110-1)*$D$62^(A110-1)</f>
         <v>0.00390625</v>
       </c>
-      <c r="C110" s="25" t="n">
+      <c r="C110" s="41" t="n">
         <f aca="false">(1-$C$62^(A110-1))*$D$62^(A110-1)</f>
         <v>0.05859375</v>
       </c>
-      <c r="D110" s="25" t="n">
+      <c r="D110" s="41" t="n">
         <f aca="false">$C$62^(A110-1)*(1-$D$62^(A110-1))</f>
         <v>0.05859375</v>
       </c>
-      <c r="E110" s="25" t="n">
+      <c r="E110" s="41" t="n">
         <f aca="false">(1-$C$62^(A110-1))*(1-$D$62^(A110-1))</f>
         <v>0.87890625</v>
       </c>
@@ -11210,19 +11219,19 @@
       <c r="A111" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B111" s="25" t="n">
+      <c r="B111" s="41" t="n">
         <f aca="false">$C$62^(A111-1)*$D$62^(A111-1)</f>
         <v>0.0009765625</v>
       </c>
-      <c r="C111" s="25" t="n">
+      <c r="C111" s="41" t="n">
         <f aca="false">(1-$C$62^(A111-1))*$D$62^(A111-1)</f>
         <v>0.0302734375</v>
       </c>
-      <c r="D111" s="25" t="n">
+      <c r="D111" s="41" t="n">
         <f aca="false">$C$62^(A111-1)*(1-$D$62^(A111-1))</f>
         <v>0.0302734375</v>
       </c>
-      <c r="E111" s="25" t="n">
+      <c r="E111" s="41" t="n">
         <f aca="false">(1-$C$62^(A111-1))*(1-$D$62^(A111-1))</f>
         <v>0.9384765625</v>
       </c>
@@ -11235,19 +11244,19 @@
       <c r="A112" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B112" s="25" t="n">
+      <c r="B112" s="41" t="n">
         <f aca="false">$C$62^(A112-1)*$D$62^(A112-1)</f>
         <v>0.000244140625</v>
       </c>
-      <c r="C112" s="25" t="n">
+      <c r="C112" s="41" t="n">
         <f aca="false">(1-$C$62^(A112-1))*$D$62^(A112-1)</f>
         <v>0.015380859375</v>
       </c>
-      <c r="D112" s="25" t="n">
+      <c r="D112" s="41" t="n">
         <f aca="false">$C$62^(A112-1)*(1-$D$62^(A112-1))</f>
         <v>0.015380859375</v>
       </c>
-      <c r="E112" s="25" t="n">
+      <c r="E112" s="41" t="n">
         <f aca="false">(1-$C$62^(A112-1))*(1-$D$62^(A112-1))</f>
         <v>0.968994140625</v>
       </c>
@@ -11260,19 +11269,19 @@
       <c r="A113" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B113" s="25" t="n">
+      <c r="B113" s="41" t="n">
         <f aca="false">$C$62^(A113-1)*$D$62^(A113-1)</f>
         <v>6.103515625E-005</v>
       </c>
-      <c r="C113" s="25" t="n">
+      <c r="C113" s="41" t="n">
         <f aca="false">(1-$C$62^(A113-1))*$D$62^(A113-1)</f>
         <v>0.00775146484375</v>
       </c>
-      <c r="D113" s="25" t="n">
+      <c r="D113" s="41" t="n">
         <f aca="false">$C$62^(A113-1)*(1-$D$62^(A113-1))</f>
         <v>0.00775146484375</v>
       </c>
-      <c r="E113" s="25" t="n">
+      <c r="E113" s="41" t="n">
         <f aca="false">(1-$C$62^(A113-1))*(1-$D$62^(A113-1))</f>
         <v>0.98443603515625</v>
       </c>
@@ -11285,19 +11294,19 @@
       <c r="A114" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B114" s="25" t="n">
+      <c r="B114" s="41" t="n">
         <f aca="false">$C$62^(A114-1)*$D$62^(A114-1)</f>
         <v>1.52587890625E-005</v>
       </c>
-      <c r="C114" s="25" t="n">
+      <c r="C114" s="41" t="n">
         <f aca="false">(1-$C$62^(A114-1))*$D$62^(A114-1)</f>
         <v>0.0038909912109375</v>
       </c>
-      <c r="D114" s="25" t="n">
+      <c r="D114" s="41" t="n">
         <f aca="false">$C$62^(A114-1)*(1-$D$62^(A114-1))</f>
         <v>0.0038909912109375</v>
       </c>
-      <c r="E114" s="25" t="n">
+      <c r="E114" s="41" t="n">
         <f aca="false">(1-$C$62^(A114-1))*(1-$D$62^(A114-1))</f>
         <v>0.992202758789063</v>
       </c>
@@ -11310,19 +11319,19 @@
       <c r="A115" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B115" s="25" t="n">
+      <c r="B115" s="41" t="n">
         <f aca="false">$C$62^(A115-1)*$D$62^(A115-1)</f>
         <v>3.814697265625E-006</v>
       </c>
-      <c r="C115" s="25" t="n">
+      <c r="C115" s="41" t="n">
         <f aca="false">(1-$C$62^(A115-1))*$D$62^(A115-1)</f>
         <v>0.00194931030273438</v>
       </c>
-      <c r="D115" s="25" t="n">
+      <c r="D115" s="41" t="n">
         <f aca="false">$C$62^(A115-1)*(1-$D$62^(A115-1))</f>
         <v>0.00194931030273438</v>
       </c>
-      <c r="E115" s="25" t="n">
+      <c r="E115" s="41" t="n">
         <f aca="false">(1-$C$62^(A115-1))*(1-$D$62^(A115-1))</f>
         <v>0.996097564697266</v>
       </c>
